--- a/public/AxisBank_Payout_Verification.xlsx
+++ b/public/AxisBank_Payout_Verification.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF53"/>
+  <dimension ref="A1:AE53"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="29"/>
     <col min="2" max="2" customWidth="1" width="29"/>
@@ -558,7 +558,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I2" t="str">
         <v>PAY20260831658011</v>
@@ -582,10 +582,10 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>PAY-20260831-658011</v>
       </c>
       <c r="Q2" t="str">
-        <v>PAY-20260831-658011</v>
+        <v/>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -627,9 +627,6 @@
         <v/>
       </c>
       <c r="AE2" t="str">
-        <v/>
-      </c>
-      <c r="AF2" t="str">
         <v/>
       </c>
     </row>
@@ -656,7 +653,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I3" t="str">
         <v>PAY20260808003115</v>
@@ -680,10 +677,10 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>PAY-20260808-003115</v>
       </c>
       <c r="Q3" t="str">
-        <v>PAY-20260808-003115</v>
+        <v/>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -725,9 +722,6 @@
         <v/>
       </c>
       <c r="AE3" t="str">
-        <v/>
-      </c>
-      <c r="AF3" t="str">
         <v/>
       </c>
     </row>
@@ -754,7 +748,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H4" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I4" t="str">
         <v>PAY20260805061816</v>
@@ -778,10 +772,10 @@
         <v/>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>PAY-20260805-061816</v>
       </c>
       <c r="Q4" t="str">
-        <v>PAY-20260805-061816</v>
+        <v/>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -823,9 +817,6 @@
         <v/>
       </c>
       <c r="AE4" t="str">
-        <v/>
-      </c>
-      <c r="AF4" t="str">
         <v/>
       </c>
     </row>
@@ -852,7 +843,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I5" t="str">
         <v>PAY20260805059908</v>
@@ -876,10 +867,10 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>PAY-20260805-059908</v>
       </c>
       <c r="Q5" t="str">
-        <v>PAY-20260805-059908</v>
+        <v/>
       </c>
       <c r="R5" t="str">
         <v/>
@@ -921,9 +912,6 @@
         <v/>
       </c>
       <c r="AE5" t="str">
-        <v/>
-      </c>
-      <c r="AF5" t="str">
         <v/>
       </c>
     </row>
@@ -950,7 +938,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H6" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I6" t="str">
         <v>PAY20260804613052</v>
@@ -974,10 +962,10 @@
         <v/>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>PAY-20260804-613052</v>
       </c>
       <c r="Q6" t="str">
-        <v>PAY-20260804-613052</v>
+        <v/>
       </c>
       <c r="R6" t="str">
         <v/>
@@ -1019,9 +1007,6 @@
         <v/>
       </c>
       <c r="AE6" t="str">
-        <v/>
-      </c>
-      <c r="AF6" t="str">
         <v/>
       </c>
     </row>
@@ -1048,7 +1033,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H7" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I7" t="str">
         <v>PAY20260804046652</v>
@@ -1072,10 +1057,10 @@
         <v/>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>PAY-20260804-046652</v>
       </c>
       <c r="Q7" t="str">
-        <v>PAY-20260804-046652</v>
+        <v/>
       </c>
       <c r="R7" t="str">
         <v/>
@@ -1117,9 +1102,6 @@
         <v/>
       </c>
       <c r="AE7" t="str">
-        <v/>
-      </c>
-      <c r="AF7" t="str">
         <v/>
       </c>
     </row>
@@ -1146,7 +1128,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H8" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I8" t="str">
         <v>PAY20260804840298</v>
@@ -1170,10 +1152,10 @@
         <v/>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>PAY-20260804-840298</v>
       </c>
       <c r="Q8" t="str">
-        <v>PAY-20260804-840298</v>
+        <v/>
       </c>
       <c r="R8" t="str">
         <v/>
@@ -1215,9 +1197,6 @@
         <v/>
       </c>
       <c r="AE8" t="str">
-        <v/>
-      </c>
-      <c r="AF8" t="str">
         <v/>
       </c>
     </row>
@@ -1244,7 +1223,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H9" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I9" t="str">
         <v>PAY20260804375695</v>
@@ -1268,10 +1247,10 @@
         <v/>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>PAY-20260804-375695</v>
       </c>
       <c r="Q9" t="str">
-        <v>PAY-20260804-375695</v>
+        <v/>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -1313,9 +1292,6 @@
         <v/>
       </c>
       <c r="AE9" t="str">
-        <v/>
-      </c>
-      <c r="AF9" t="str">
         <v/>
       </c>
     </row>
@@ -1342,7 +1318,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H10" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I10" t="str">
         <v>PAY20260804451179</v>
@@ -1366,10 +1342,10 @@
         <v/>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>PAY-20260804-451179</v>
       </c>
       <c r="Q10" t="str">
-        <v>PAY-20260804-451179</v>
+        <v/>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -1411,9 +1387,6 @@
         <v/>
       </c>
       <c r="AE10" t="str">
-        <v/>
-      </c>
-      <c r="AF10" t="str">
         <v/>
       </c>
     </row>
@@ -1440,7 +1413,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H11" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I11" t="str">
         <v>PAY20260804546420</v>
@@ -1464,10 +1437,10 @@
         <v/>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>PAY-20260804-546420</v>
       </c>
       <c r="Q11" t="str">
-        <v>PAY-20260804-546420</v>
+        <v/>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -1509,9 +1482,6 @@
         <v/>
       </c>
       <c r="AE11" t="str">
-        <v/>
-      </c>
-      <c r="AF11" t="str">
         <v/>
       </c>
     </row>
@@ -1538,7 +1508,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H12" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I12" t="str">
         <v>PAY20260804405930</v>
@@ -1562,10 +1532,10 @@
         <v/>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>PAY-20260804-405930</v>
       </c>
       <c r="Q12" t="str">
-        <v>PAY-20260804-405930</v>
+        <v/>
       </c>
       <c r="R12" t="str">
         <v/>
@@ -1607,9 +1577,6 @@
         <v/>
       </c>
       <c r="AE12" t="str">
-        <v/>
-      </c>
-      <c r="AF12" t="str">
         <v/>
       </c>
     </row>
@@ -1636,7 +1603,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H13" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I13" t="str">
         <v>PAY20260802315857</v>
@@ -1660,10 +1627,10 @@
         <v/>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>PAY-20260802-315857</v>
       </c>
       <c r="Q13" t="str">
-        <v>PAY-20260802-315857</v>
+        <v/>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -1705,9 +1672,6 @@
         <v/>
       </c>
       <c r="AE13" t="str">
-        <v/>
-      </c>
-      <c r="AF13" t="str">
         <v/>
       </c>
     </row>
@@ -1734,7 +1698,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H14" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I14" t="str">
         <v>PAY20260801933762</v>
@@ -1758,10 +1722,10 @@
         <v/>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>PAY-20260801-933762</v>
       </c>
       <c r="Q14" t="str">
-        <v>PAY-20260801-933762</v>
+        <v/>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -1803,9 +1767,6 @@
         <v/>
       </c>
       <c r="AE14" t="str">
-        <v/>
-      </c>
-      <c r="AF14" t="str">
         <v/>
       </c>
     </row>
@@ -1832,7 +1793,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H15" t="str">
-        <v>RTGS</v>
+        <v>R</v>
       </c>
       <c r="I15" t="str">
         <v>PAY20260801762336</v>
@@ -1856,10 +1817,10 @@
         <v/>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>PAY-20260801-762336</v>
       </c>
       <c r="Q15" t="str">
-        <v>PAY-20260801-762336</v>
+        <v/>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -1901,9 +1862,6 @@
         <v/>
       </c>
       <c r="AE15" t="str">
-        <v/>
-      </c>
-      <c r="AF15" t="str">
         <v/>
       </c>
     </row>
@@ -1930,7 +1888,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H16" t="str">
-        <v>RTGS</v>
+        <v>R</v>
       </c>
       <c r="I16" t="str">
         <v>PAY20260731875317</v>
@@ -1954,10 +1912,10 @@
         <v/>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>PAY-20260731-875317</v>
       </c>
       <c r="Q16" t="str">
-        <v>PAY-20260731-875317</v>
+        <v/>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -1999,9 +1957,6 @@
         <v/>
       </c>
       <c r="AE16" t="str">
-        <v/>
-      </c>
-      <c r="AF16" t="str">
         <v/>
       </c>
     </row>
@@ -2028,7 +1983,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H17" t="str">
-        <v>RTGS</v>
+        <v>R</v>
       </c>
       <c r="I17" t="str">
         <v>PAY20260731912652</v>
@@ -2052,10 +2007,10 @@
         <v/>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>PAY-20260731-912652</v>
       </c>
       <c r="Q17" t="str">
-        <v>PAY-20260731-912652</v>
+        <v/>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -2097,9 +2052,6 @@
         <v/>
       </c>
       <c r="AE17" t="str">
-        <v/>
-      </c>
-      <c r="AF17" t="str">
         <v/>
       </c>
     </row>
@@ -2126,7 +2078,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H18" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I18" t="str">
         <v>PAY20260731523707</v>
@@ -2150,10 +2102,10 @@
         <v/>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>PAY-20260731-523707</v>
       </c>
       <c r="Q18" t="str">
-        <v>PAY-20260731-523707</v>
+        <v/>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -2195,9 +2147,6 @@
         <v/>
       </c>
       <c r="AE18" t="str">
-        <v/>
-      </c>
-      <c r="AF18" t="str">
         <v/>
       </c>
     </row>
@@ -2224,7 +2173,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H19" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I19" t="str">
         <v>PAY20260731578132</v>
@@ -2248,10 +2197,10 @@
         <v/>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>PAY-20260731-578132</v>
       </c>
       <c r="Q19" t="str">
-        <v>PAY-20260731-578132</v>
+        <v/>
       </c>
       <c r="R19" t="str">
         <v/>
@@ -2293,9 +2242,6 @@
         <v/>
       </c>
       <c r="AE19" t="str">
-        <v/>
-      </c>
-      <c r="AF19" t="str">
         <v/>
       </c>
     </row>
@@ -2322,7 +2268,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H20" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I20" t="str">
         <v>PAY20260730226073</v>
@@ -2346,10 +2292,10 @@
         <v/>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>PAY-20260730-226073</v>
       </c>
       <c r="Q20" t="str">
-        <v>PAY-20260730-226073</v>
+        <v/>
       </c>
       <c r="R20" t="str">
         <v/>
@@ -2391,9 +2337,6 @@
         <v/>
       </c>
       <c r="AE20" t="str">
-        <v/>
-      </c>
-      <c r="AF20" t="str">
         <v/>
       </c>
     </row>
@@ -2420,7 +2363,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H21" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I21" t="str">
         <v>PAY20260730913804</v>
@@ -2444,10 +2387,10 @@
         <v/>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>PAY-20260730-913804</v>
       </c>
       <c r="Q21" t="str">
-        <v>PAY-20260730-913804</v>
+        <v/>
       </c>
       <c r="R21" t="str">
         <v/>
@@ -2489,9 +2432,6 @@
         <v/>
       </c>
       <c r="AE21" t="str">
-        <v/>
-      </c>
-      <c r="AF21" t="str">
         <v/>
       </c>
     </row>
@@ -2518,7 +2458,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H22" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I22" t="str">
         <v>PAY20260730456908</v>
@@ -2542,10 +2482,10 @@
         <v/>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>PAY-20260730-456908</v>
       </c>
       <c r="Q22" t="str">
-        <v>PAY-20260730-456908</v>
+        <v/>
       </c>
       <c r="R22" t="str">
         <v/>
@@ -2587,9 +2527,6 @@
         <v/>
       </c>
       <c r="AE22" t="str">
-        <v/>
-      </c>
-      <c r="AF22" t="str">
         <v/>
       </c>
     </row>
@@ -2616,7 +2553,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H23" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I23" t="str">
         <v>PAY20260730386586</v>
@@ -2640,10 +2577,10 @@
         <v/>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>PAY-20260730-386586</v>
       </c>
       <c r="Q23" t="str">
-        <v>PAY-20260730-386586</v>
+        <v/>
       </c>
       <c r="R23" t="str">
         <v/>
@@ -2685,9 +2622,6 @@
         <v/>
       </c>
       <c r="AE23" t="str">
-        <v/>
-      </c>
-      <c r="AF23" t="str">
         <v/>
       </c>
     </row>
@@ -2714,7 +2648,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H24" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I24" t="str">
         <v>PAY20260729419157</v>
@@ -2738,10 +2672,10 @@
         <v/>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>PAY-20260729-419157</v>
       </c>
       <c r="Q24" t="str">
-        <v>PAY-20260729-419157</v>
+        <v/>
       </c>
       <c r="R24" t="str">
         <v/>
@@ -2783,9 +2717,6 @@
         <v/>
       </c>
       <c r="AE24" t="str">
-        <v/>
-      </c>
-      <c r="AF24" t="str">
         <v/>
       </c>
     </row>
@@ -2812,7 +2743,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H25" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I25" t="str">
         <v>PAY20260729438891</v>
@@ -2836,10 +2767,10 @@
         <v/>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>PAY-20260729-438891</v>
       </c>
       <c r="Q25" t="str">
-        <v>PAY-20260729-438891</v>
+        <v/>
       </c>
       <c r="R25" t="str">
         <v/>
@@ -2881,9 +2812,6 @@
         <v/>
       </c>
       <c r="AE25" t="str">
-        <v/>
-      </c>
-      <c r="AF25" t="str">
         <v/>
       </c>
     </row>
@@ -2910,7 +2838,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H26" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I26" t="str">
         <v>PAY20260729580331</v>
@@ -2934,10 +2862,10 @@
         <v/>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>PAY-20260729-580331</v>
       </c>
       <c r="Q26" t="str">
-        <v>PAY-20260729-580331</v>
+        <v/>
       </c>
       <c r="R26" t="str">
         <v/>
@@ -2979,9 +2907,6 @@
         <v/>
       </c>
       <c r="AE26" t="str">
-        <v/>
-      </c>
-      <c r="AF26" t="str">
         <v/>
       </c>
     </row>
@@ -3008,7 +2933,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H27" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I27" t="str">
         <v>PAY20260729383214</v>
@@ -3032,10 +2957,10 @@
         <v/>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>PAY-20260729-383214</v>
       </c>
       <c r="Q27" t="str">
-        <v>PAY-20260729-383214</v>
+        <v/>
       </c>
       <c r="R27" t="str">
         <v/>
@@ -3077,9 +3002,6 @@
         <v/>
       </c>
       <c r="AE27" t="str">
-        <v/>
-      </c>
-      <c r="AF27" t="str">
         <v/>
       </c>
     </row>
@@ -3106,7 +3028,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H28" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I28" t="str">
         <v>PAY20260729258687</v>
@@ -3130,10 +3052,10 @@
         <v/>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>PAY-20260729-258687</v>
       </c>
       <c r="Q28" t="str">
-        <v>PAY-20260729-258687</v>
+        <v/>
       </c>
       <c r="R28" t="str">
         <v/>
@@ -3175,9 +3097,6 @@
         <v/>
       </c>
       <c r="AE28" t="str">
-        <v/>
-      </c>
-      <c r="AF28" t="str">
         <v/>
       </c>
     </row>
@@ -3204,7 +3123,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H29" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I29" t="str">
         <v>PAY20260729476921</v>
@@ -3228,10 +3147,10 @@
         <v/>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>PAY-20260729-476921</v>
       </c>
       <c r="Q29" t="str">
-        <v>PAY-20260729-476921</v>
+        <v/>
       </c>
       <c r="R29" t="str">
         <v/>
@@ -3273,9 +3192,6 @@
         <v/>
       </c>
       <c r="AE29" t="str">
-        <v/>
-      </c>
-      <c r="AF29" t="str">
         <v/>
       </c>
     </row>
@@ -3302,7 +3218,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H30" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I30" t="str">
         <v>PAY20260729338238</v>
@@ -3326,10 +3242,10 @@
         <v/>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>PAY-20260729-338238</v>
       </c>
       <c r="Q30" t="str">
-        <v>PAY-20260729-338238</v>
+        <v/>
       </c>
       <c r="R30" t="str">
         <v/>
@@ -3371,9 +3287,6 @@
         <v/>
       </c>
       <c r="AE30" t="str">
-        <v/>
-      </c>
-      <c r="AF30" t="str">
         <v/>
       </c>
     </row>
@@ -3400,7 +3313,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H31" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I31" t="str">
         <v>PAY20260729529558</v>
@@ -3424,10 +3337,10 @@
         <v/>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>PAY-20260729-529558</v>
       </c>
       <c r="Q31" t="str">
-        <v>PAY-20260729-529558</v>
+        <v/>
       </c>
       <c r="R31" t="str">
         <v/>
@@ -3469,9 +3382,6 @@
         <v/>
       </c>
       <c r="AE31" t="str">
-        <v/>
-      </c>
-      <c r="AF31" t="str">
         <v/>
       </c>
     </row>
@@ -3498,7 +3408,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H32" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I32" t="str">
         <v>PAY20260728715352</v>
@@ -3522,10 +3432,10 @@
         <v/>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>PAY-20260728-715352</v>
       </c>
       <c r="Q32" t="str">
-        <v>PAY-20260728-715352</v>
+        <v/>
       </c>
       <c r="R32" t="str">
         <v/>
@@ -3567,9 +3477,6 @@
         <v/>
       </c>
       <c r="AE32" t="str">
-        <v/>
-      </c>
-      <c r="AF32" t="str">
         <v/>
       </c>
     </row>
@@ -3596,7 +3503,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H33" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I33" t="str">
         <v>PAY20260727064276</v>
@@ -3620,10 +3527,10 @@
         <v/>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>PAY-20260727-064276</v>
       </c>
       <c r="Q33" t="str">
-        <v>PAY-20260727-064276</v>
+        <v/>
       </c>
       <c r="R33" t="str">
         <v/>
@@ -3665,9 +3572,6 @@
         <v/>
       </c>
       <c r="AE33" t="str">
-        <v/>
-      </c>
-      <c r="AF33" t="str">
         <v/>
       </c>
     </row>
@@ -3694,7 +3598,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H34" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I34" t="str">
         <v>PAY20260721460795</v>
@@ -3718,10 +3622,10 @@
         <v/>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>PAY-20260721-460795</v>
       </c>
       <c r="Q34" t="str">
-        <v>PAY-20260721-460795</v>
+        <v/>
       </c>
       <c r="R34" t="str">
         <v/>
@@ -3763,9 +3667,6 @@
         <v/>
       </c>
       <c r="AE34" t="str">
-        <v/>
-      </c>
-      <c r="AF34" t="str">
         <v/>
       </c>
     </row>
@@ -3792,7 +3693,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H35" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I35" t="str">
         <v>PAY20260716622742</v>
@@ -3816,10 +3717,10 @@
         <v/>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>PAY-20260716-622742</v>
       </c>
       <c r="Q35" t="str">
-        <v>PAY-20260716-622742</v>
+        <v/>
       </c>
       <c r="R35" t="str">
         <v/>
@@ -3861,9 +3762,6 @@
         <v/>
       </c>
       <c r="AE35" t="str">
-        <v/>
-      </c>
-      <c r="AF35" t="str">
         <v/>
       </c>
     </row>
@@ -3890,7 +3788,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H36" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I36" t="str">
         <v>PAY20260716725492</v>
@@ -3914,10 +3812,10 @@
         <v/>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>PAY-20260716-725492</v>
       </c>
       <c r="Q36" t="str">
-        <v>PAY-20260716-725492</v>
+        <v/>
       </c>
       <c r="R36" t="str">
         <v/>
@@ -3959,9 +3857,6 @@
         <v/>
       </c>
       <c r="AE36" t="str">
-        <v/>
-      </c>
-      <c r="AF36" t="str">
         <v/>
       </c>
     </row>
@@ -3988,7 +3883,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H37" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I37" t="str">
         <v>PAY20260716075298</v>
@@ -4012,10 +3907,10 @@
         <v/>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>PAY-20260716-075298</v>
       </c>
       <c r="Q37" t="str">
-        <v>PAY-20260716-075298</v>
+        <v/>
       </c>
       <c r="R37" t="str">
         <v/>
@@ -4057,9 +3952,6 @@
         <v/>
       </c>
       <c r="AE37" t="str">
-        <v/>
-      </c>
-      <c r="AF37" t="str">
         <v/>
       </c>
     </row>
@@ -4086,7 +3978,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H38" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I38" t="str">
         <v>PAY20260716247057</v>
@@ -4110,10 +4002,10 @@
         <v/>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>PAY-20260716-247057</v>
       </c>
       <c r="Q38" t="str">
-        <v>PAY-20260716-247057</v>
+        <v/>
       </c>
       <c r="R38" t="str">
         <v/>
@@ -4155,9 +4047,6 @@
         <v/>
       </c>
       <c r="AE38" t="str">
-        <v/>
-      </c>
-      <c r="AF38" t="str">
         <v/>
       </c>
     </row>
@@ -4184,7 +4073,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H39" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I39" t="str">
         <v>PAY20260716168456</v>
@@ -4208,10 +4097,10 @@
         <v/>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>PAY-20260716-168456</v>
       </c>
       <c r="Q39" t="str">
-        <v>PAY-20260716-168456</v>
+        <v/>
       </c>
       <c r="R39" t="str">
         <v/>
@@ -4253,9 +4142,6 @@
         <v/>
       </c>
       <c r="AE39" t="str">
-        <v/>
-      </c>
-      <c r="AF39" t="str">
         <v/>
       </c>
     </row>
@@ -4282,7 +4168,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H40" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I40" t="str">
         <v>PAY20260716097378</v>
@@ -4306,10 +4192,10 @@
         <v/>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>PAY-20260716-097378</v>
       </c>
       <c r="Q40" t="str">
-        <v>PAY-20260716-097378</v>
+        <v/>
       </c>
       <c r="R40" t="str">
         <v/>
@@ -4351,9 +4237,6 @@
         <v/>
       </c>
       <c r="AE40" t="str">
-        <v/>
-      </c>
-      <c r="AF40" t="str">
         <v/>
       </c>
     </row>
@@ -4380,7 +4263,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H41" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I41" t="str">
         <v>PAY20260711958193</v>
@@ -4404,10 +4287,10 @@
         <v/>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>PAY-20260711-958193</v>
       </c>
       <c r="Q41" t="str">
-        <v>PAY-20260711-958193</v>
+        <v/>
       </c>
       <c r="R41" t="str">
         <v/>
@@ -4449,9 +4332,6 @@
         <v/>
       </c>
       <c r="AE41" t="str">
-        <v/>
-      </c>
-      <c r="AF41" t="str">
         <v/>
       </c>
     </row>
@@ -4478,7 +4358,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H42" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I42" t="str">
         <v>PAY20260708826638</v>
@@ -4502,10 +4382,10 @@
         <v/>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>PAY-20260708-826638</v>
       </c>
       <c r="Q42" t="str">
-        <v>PAY-20260708-826638</v>
+        <v/>
       </c>
       <c r="R42" t="str">
         <v/>
@@ -4547,9 +4427,6 @@
         <v/>
       </c>
       <c r="AE42" t="str">
-        <v/>
-      </c>
-      <c r="AF42" t="str">
         <v/>
       </c>
     </row>
@@ -4576,7 +4453,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H43" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I43" t="str">
         <v>PAY20260708863377</v>
@@ -4600,10 +4477,10 @@
         <v/>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>PAY-20260708-863377</v>
       </c>
       <c r="Q43" t="str">
-        <v>PAY-20260708-863377</v>
+        <v/>
       </c>
       <c r="R43" t="str">
         <v/>
@@ -4645,9 +4522,6 @@
         <v/>
       </c>
       <c r="AE43" t="str">
-        <v/>
-      </c>
-      <c r="AF43" t="str">
         <v/>
       </c>
     </row>
@@ -4674,7 +4548,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H44" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I44" t="str">
         <v>PAY20260708320378</v>
@@ -4698,10 +4572,10 @@
         <v/>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>PAY-20260708-320378</v>
       </c>
       <c r="Q44" t="str">
-        <v>PAY-20260708-320378</v>
+        <v/>
       </c>
       <c r="R44" t="str">
         <v/>
@@ -4743,9 +4617,6 @@
         <v/>
       </c>
       <c r="AE44" t="str">
-        <v/>
-      </c>
-      <c r="AF44" t="str">
         <v/>
       </c>
     </row>
@@ -4772,7 +4643,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H45" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I45" t="str">
         <v>PAY20260708088577</v>
@@ -4796,10 +4667,10 @@
         <v/>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>PAY-20260708-088577</v>
       </c>
       <c r="Q45" t="str">
-        <v>PAY-20260708-088577</v>
+        <v/>
       </c>
       <c r="R45" t="str">
         <v/>
@@ -4841,9 +4712,6 @@
         <v/>
       </c>
       <c r="AE45" t="str">
-        <v/>
-      </c>
-      <c r="AF45" t="str">
         <v/>
       </c>
     </row>
@@ -4870,7 +4738,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H46" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I46" t="str">
         <v>PAY20260708050762</v>
@@ -4894,10 +4762,10 @@
         <v/>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>PAY-20260708-050762</v>
       </c>
       <c r="Q46" t="str">
-        <v>PAY-20260708-050762</v>
+        <v/>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -4939,9 +4807,6 @@
         <v/>
       </c>
       <c r="AE46" t="str">
-        <v/>
-      </c>
-      <c r="AF46" t="str">
         <v/>
       </c>
     </row>
@@ -4968,7 +4833,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H47" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I47" t="str">
         <v>PAY20260707269449</v>
@@ -4992,10 +4857,10 @@
         <v/>
       </c>
       <c r="P47" t="str">
-        <v/>
+        <v>PAY-20260707-269449</v>
       </c>
       <c r="Q47" t="str">
-        <v>PAY-20260707-269449</v>
+        <v/>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -5037,9 +4902,6 @@
         <v/>
       </c>
       <c r="AE47" t="str">
-        <v/>
-      </c>
-      <c r="AF47" t="str">
         <v/>
       </c>
     </row>
@@ -5066,7 +4928,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H48" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I48" t="str">
         <v>PAY20260701805832</v>
@@ -5090,10 +4952,10 @@
         <v/>
       </c>
       <c r="P48" t="str">
-        <v/>
+        <v>PAY-20260701-805832</v>
       </c>
       <c r="Q48" t="str">
-        <v>PAY-20260701-805832</v>
+        <v/>
       </c>
       <c r="R48" t="str">
         <v/>
@@ -5135,9 +4997,6 @@
         <v/>
       </c>
       <c r="AE48" t="str">
-        <v/>
-      </c>
-      <c r="AF48" t="str">
         <v/>
       </c>
     </row>
@@ -5164,7 +5023,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H49" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I49" t="str">
         <v>PAY20260701319443</v>
@@ -5188,10 +5047,10 @@
         <v/>
       </c>
       <c r="P49" t="str">
-        <v/>
+        <v>PAY-20260701-319443</v>
       </c>
       <c r="Q49" t="str">
-        <v>PAY-20260701-319443</v>
+        <v/>
       </c>
       <c r="R49" t="str">
         <v/>
@@ -5233,9 +5092,6 @@
         <v/>
       </c>
       <c r="AE49" t="str">
-        <v/>
-      </c>
-      <c r="AF49" t="str">
         <v/>
       </c>
     </row>
@@ -5262,7 +5118,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H50" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I50" t="str">
         <v>PAY20260616951859</v>
@@ -5286,10 +5142,10 @@
         <v/>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>PAY-20260616-951859</v>
       </c>
       <c r="Q50" t="str">
-        <v>PAY-20260616-951859</v>
+        <v/>
       </c>
       <c r="R50" t="str">
         <v/>
@@ -5331,9 +5187,6 @@
         <v/>
       </c>
       <c r="AE50" t="str">
-        <v/>
-      </c>
-      <c r="AF50" t="str">
         <v/>
       </c>
     </row>
@@ -5360,7 +5213,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H51" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I51" t="str">
         <v>PAY20260616469779</v>
@@ -5384,10 +5237,10 @@
         <v/>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>PAY-20260616-469779</v>
       </c>
       <c r="Q51" t="str">
-        <v>PAY-20260616-469779</v>
+        <v/>
       </c>
       <c r="R51" t="str">
         <v/>
@@ -5429,9 +5282,6 @@
         <v/>
       </c>
       <c r="AE51" t="str">
-        <v/>
-      </c>
-      <c r="AF51" t="str">
         <v/>
       </c>
     </row>
@@ -5458,7 +5308,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H52" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I52" t="str">
         <v>PAY20260616172942</v>
@@ -5482,10 +5332,10 @@
         <v/>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>PAY-20260616-172942</v>
       </c>
       <c r="Q52" t="str">
-        <v>PAY-20260616-172942</v>
+        <v/>
       </c>
       <c r="R52" t="str">
         <v/>
@@ -5527,9 +5377,6 @@
         <v/>
       </c>
       <c r="AE52" t="str">
-        <v/>
-      </c>
-      <c r="AF52" t="str">
         <v/>
       </c>
     </row>
@@ -5556,7 +5403,7 @@
         <v>04/09/2026</v>
       </c>
       <c r="H53" t="str">
-        <v>NEFT</v>
+        <v>N</v>
       </c>
       <c r="I53" t="str">
         <v>PAY20260616639105</v>
@@ -5580,10 +5427,10 @@
         <v/>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>PAY-20260616-639105</v>
       </c>
       <c r="Q53" t="str">
-        <v>PAY-20260616-639105</v>
+        <v/>
       </c>
       <c r="R53" t="str">
         <v/>
@@ -5625,16 +5472,13 @@
         <v/>
       </c>
       <c r="AE53" t="str">
-        <v/>
-      </c>
-      <c r="AF53" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AF53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE53"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/AxisBank_Payout_Verification.xlsx
+++ b/public/AxisBank_Payout_Verification.xlsx
@@ -555,7 +555,7 @@
         <v>SBIN0002571</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H2" t="str">
         <v>N</v>
@@ -576,13 +576,13 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>PAY-20260831-658011</v>
       </c>
       <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>PAY-20260831-658011</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -650,7 +650,7 @@
         <v>BKID0000083</v>
       </c>
       <c r="G3" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H3" t="str">
         <v>N</v>
@@ -671,13 +671,13 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>PAY-20260808-003115</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>PAY-20260808-003115</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
         <v/>
@@ -745,7 +745,7 @@
         <v>SBIN0005794</v>
       </c>
       <c r="G4" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H4" t="str">
         <v>N</v>
@@ -766,13 +766,13 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>PAY-20260805-061816</v>
       </c>
       <c r="O4" t="str">
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>PAY-20260805-061816</v>
+        <v/>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -840,7 +840,7 @@
         <v>HDFC0000485</v>
       </c>
       <c r="G5" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H5" t="str">
         <v>N</v>
@@ -861,13 +861,13 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>PAY-20260805-059908</v>
       </c>
       <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>PAY-20260805-059908</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
         <v/>
@@ -935,7 +935,7 @@
         <v>HDFC0002870</v>
       </c>
       <c r="G6" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H6" t="str">
         <v>N</v>
@@ -956,13 +956,13 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>PAY-20260804-613052</v>
       </c>
       <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>PAY-20260804-613052</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -1030,7 +1030,7 @@
         <v>HDFC0000729</v>
       </c>
       <c r="G7" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H7" t="str">
         <v>N</v>
@@ -1051,13 +1051,13 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>PAY-20260804-046652</v>
       </c>
       <c r="O7" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>PAY-20260804-046652</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
         <v/>
@@ -1125,10 +1125,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G8" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H8" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I8" t="str">
         <v>PAY20260804840298</v>
@@ -1146,13 +1146,13 @@
         <v/>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>PAY-20260804-840298</v>
       </c>
       <c r="O8" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>PAY-20260804-840298</v>
+        <v/>
       </c>
       <c r="Q8" t="str">
         <v/>
@@ -1220,7 +1220,7 @@
         <v>JIOP0000001</v>
       </c>
       <c r="G9" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H9" t="str">
         <v>N</v>
@@ -1241,13 +1241,13 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>PAY-20260804-375695</v>
       </c>
       <c r="O9" t="str">
         <v/>
       </c>
       <c r="P9" t="str">
-        <v>PAY-20260804-375695</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
         <v/>
@@ -1315,7 +1315,7 @@
         <v>JIOP0000001</v>
       </c>
       <c r="G10" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H10" t="str">
         <v>N</v>
@@ -1336,13 +1336,13 @@
         <v/>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>PAY-20260804-451179</v>
       </c>
       <c r="O10" t="str">
         <v/>
       </c>
       <c r="P10" t="str">
-        <v>PAY-20260804-451179</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
         <v/>
@@ -1410,7 +1410,7 @@
         <v>HDFC0000729</v>
       </c>
       <c r="G11" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H11" t="str">
         <v>N</v>
@@ -1431,13 +1431,13 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>PAY-20260804-546420</v>
       </c>
       <c r="O11" t="str">
         <v/>
       </c>
       <c r="P11" t="str">
-        <v>PAY-20260804-546420</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
         <v/>
@@ -1505,7 +1505,7 @@
         <v>SBIN0005794</v>
       </c>
       <c r="G12" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H12" t="str">
         <v>N</v>
@@ -1526,13 +1526,13 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>PAY-20260804-405930</v>
       </c>
       <c r="O12" t="str">
         <v/>
       </c>
       <c r="P12" t="str">
-        <v>PAY-20260804-405930</v>
+        <v/>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -1600,7 +1600,7 @@
         <v>ICIC0000946</v>
       </c>
       <c r="G13" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H13" t="str">
         <v>N</v>
@@ -1621,13 +1621,13 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>PAY-20260802-315857</v>
       </c>
       <c r="O13" t="str">
         <v/>
       </c>
       <c r="P13" t="str">
-        <v>PAY-20260802-315857</v>
+        <v/>
       </c>
       <c r="Q13" t="str">
         <v/>
@@ -1695,7 +1695,7 @@
         <v>CNRB0013128</v>
       </c>
       <c r="G14" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H14" t="str">
         <v>N</v>
@@ -1716,13 +1716,13 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>PAY-20260801-933762</v>
       </c>
       <c r="O14" t="str">
         <v/>
       </c>
       <c r="P14" t="str">
-        <v>PAY-20260801-933762</v>
+        <v/>
       </c>
       <c r="Q14" t="str">
         <v/>
@@ -1790,7 +1790,7 @@
         <v>CNRB0013128</v>
       </c>
       <c r="G15" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H15" t="str">
         <v>R</v>
@@ -1811,13 +1811,13 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>PAY-20260801-762336</v>
       </c>
       <c r="O15" t="str">
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>PAY-20260801-762336</v>
+        <v/>
       </c>
       <c r="Q15" t="str">
         <v/>
@@ -1885,7 +1885,7 @@
         <v>CNRB0013128</v>
       </c>
       <c r="G16" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H16" t="str">
         <v>R</v>
@@ -1906,13 +1906,13 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>PAY-20260731-875317</v>
       </c>
       <c r="O16" t="str">
         <v/>
       </c>
       <c r="P16" t="str">
-        <v>PAY-20260731-875317</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
         <v/>
@@ -1980,7 +1980,7 @@
         <v>CNRB0013128</v>
       </c>
       <c r="G17" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H17" t="str">
         <v>R</v>
@@ -2001,13 +2001,13 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>PAY-20260731-912652</v>
       </c>
       <c r="O17" t="str">
         <v/>
       </c>
       <c r="P17" t="str">
-        <v>PAY-20260731-912652</v>
+        <v/>
       </c>
       <c r="Q17" t="str">
         <v/>
@@ -2075,7 +2075,7 @@
         <v>SBIN00CARDS</v>
       </c>
       <c r="G18" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H18" t="str">
         <v>N</v>
@@ -2096,13 +2096,13 @@
         <v/>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>PAY-20260731-523707</v>
       </c>
       <c r="O18" t="str">
         <v/>
       </c>
       <c r="P18" t="str">
-        <v>PAY-20260731-523707</v>
+        <v/>
       </c>
       <c r="Q18" t="str">
         <v/>
@@ -2170,7 +2170,7 @@
         <v>HDFC0002578</v>
       </c>
       <c r="G19" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H19" t="str">
         <v>N</v>
@@ -2191,13 +2191,13 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>PAY-20260731-578132</v>
       </c>
       <c r="O19" t="str">
         <v/>
       </c>
       <c r="P19" t="str">
-        <v>PAY-20260731-578132</v>
+        <v/>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -2265,7 +2265,7 @@
         <v>ICIC0000946</v>
       </c>
       <c r="G20" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H20" t="str">
         <v>N</v>
@@ -2286,13 +2286,13 @@
         <v/>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>PAY-20260730-226073</v>
       </c>
       <c r="O20" t="str">
         <v/>
       </c>
       <c r="P20" t="str">
-        <v>PAY-20260730-226073</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
         <v/>
@@ -2360,7 +2360,7 @@
         <v>ICIC0000946</v>
       </c>
       <c r="G21" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H21" t="str">
         <v>N</v>
@@ -2381,13 +2381,13 @@
         <v/>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>PAY-20260730-913804</v>
       </c>
       <c r="O21" t="str">
         <v/>
       </c>
       <c r="P21" t="str">
-        <v>PAY-20260730-913804</v>
+        <v/>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -2455,7 +2455,7 @@
         <v>HDFC0002578</v>
       </c>
       <c r="G22" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H22" t="str">
         <v>N</v>
@@ -2476,13 +2476,13 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>PAY-20260730-456908</v>
       </c>
       <c r="O22" t="str">
         <v/>
       </c>
       <c r="P22" t="str">
-        <v>PAY-20260730-456908</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
         <v/>
@@ -2550,7 +2550,7 @@
         <v>SBIN0000055</v>
       </c>
       <c r="G23" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H23" t="str">
         <v>N</v>
@@ -2571,13 +2571,13 @@
         <v/>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>PAY-20260730-386586</v>
       </c>
       <c r="O23" t="str">
         <v/>
       </c>
       <c r="P23" t="str">
-        <v>PAY-20260730-386586</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
         <v/>
@@ -2645,7 +2645,7 @@
         <v>IDFB0081813</v>
       </c>
       <c r="G24" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H24" t="str">
         <v>N</v>
@@ -2666,13 +2666,13 @@
         <v/>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>PAY-20260729-419157</v>
       </c>
       <c r="O24" t="str">
         <v/>
       </c>
       <c r="P24" t="str">
-        <v>PAY-20260729-419157</v>
+        <v/>
       </c>
       <c r="Q24" t="str">
         <v/>
@@ -2740,7 +2740,7 @@
         <v>IDFB0081813</v>
       </c>
       <c r="G25" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H25" t="str">
         <v>N</v>
@@ -2761,13 +2761,13 @@
         <v/>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>PAY-20260729-438891</v>
       </c>
       <c r="O25" t="str">
         <v/>
       </c>
       <c r="P25" t="str">
-        <v>PAY-20260729-438891</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
         <v/>
@@ -2835,7 +2835,7 @@
         <v>IDFB0081813</v>
       </c>
       <c r="G26" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H26" t="str">
         <v>N</v>
@@ -2856,13 +2856,13 @@
         <v/>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>PAY-20260729-580331</v>
       </c>
       <c r="O26" t="str">
         <v/>
       </c>
       <c r="P26" t="str">
-        <v>PAY-20260729-580331</v>
+        <v/>
       </c>
       <c r="Q26" t="str">
         <v/>
@@ -2930,7 +2930,7 @@
         <v>ICIC0006310</v>
       </c>
       <c r="G27" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H27" t="str">
         <v>N</v>
@@ -2951,13 +2951,13 @@
         <v/>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>PAY-20260729-383214</v>
       </c>
       <c r="O27" t="str">
         <v/>
       </c>
       <c r="P27" t="str">
-        <v>PAY-20260729-383214</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
         <v/>
@@ -3025,7 +3025,7 @@
         <v>ICIC0006310</v>
       </c>
       <c r="G28" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H28" t="str">
         <v>N</v>
@@ -3046,13 +3046,13 @@
         <v/>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>PAY-20260729-258687</v>
       </c>
       <c r="O28" t="str">
         <v/>
       </c>
       <c r="P28" t="str">
-        <v>PAY-20260729-258687</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
         <v/>
@@ -3120,7 +3120,7 @@
         <v>ICIC0006310</v>
       </c>
       <c r="G29" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H29" t="str">
         <v>N</v>
@@ -3141,13 +3141,13 @@
         <v/>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>PAY-20260729-476921</v>
       </c>
       <c r="O29" t="str">
         <v/>
       </c>
       <c r="P29" t="str">
-        <v>PAY-20260729-476921</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
         <v/>
@@ -3215,10 +3215,10 @@
         <v>UTIB0002070</v>
       </c>
       <c r="G30" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H30" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I30" t="str">
         <v>PAY20260729338238</v>
@@ -3236,13 +3236,13 @@
         <v/>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>PAY-20260729-338238</v>
       </c>
       <c r="O30" t="str">
         <v/>
       </c>
       <c r="P30" t="str">
-        <v>PAY-20260729-338238</v>
+        <v/>
       </c>
       <c r="Q30" t="str">
         <v/>
@@ -3310,7 +3310,7 @@
         <v>SBIN0000055</v>
       </c>
       <c r="G31" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H31" t="str">
         <v>N</v>
@@ -3331,13 +3331,13 @@
         <v/>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>PAY-20260729-529558</v>
       </c>
       <c r="O31" t="str">
         <v/>
       </c>
       <c r="P31" t="str">
-        <v>PAY-20260729-529558</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
         <v/>
@@ -3405,10 +3405,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G32" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H32" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I32" t="str">
         <v>PAY20260728715352</v>
@@ -3426,13 +3426,13 @@
         <v/>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>PAY-20260728-715352</v>
       </c>
       <c r="O32" t="str">
         <v/>
       </c>
       <c r="P32" t="str">
-        <v>PAY-20260728-715352</v>
+        <v/>
       </c>
       <c r="Q32" t="str">
         <v/>
@@ -3500,10 +3500,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G33" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H33" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I33" t="str">
         <v>PAY20260727064276</v>
@@ -3521,13 +3521,13 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v/>
+        <v>PAY-20260727-064276</v>
       </c>
       <c r="O33" t="str">
         <v/>
       </c>
       <c r="P33" t="str">
-        <v>PAY-20260727-064276</v>
+        <v/>
       </c>
       <c r="Q33" t="str">
         <v/>
@@ -3595,7 +3595,7 @@
         <v>ICIC0000169</v>
       </c>
       <c r="G34" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H34" t="str">
         <v>N</v>
@@ -3616,13 +3616,13 @@
         <v/>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>PAY-20260721-460795</v>
       </c>
       <c r="O34" t="str">
         <v/>
       </c>
       <c r="P34" t="str">
-        <v>PAY-20260721-460795</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
         <v/>
@@ -3690,10 +3690,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G35" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H35" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I35" t="str">
         <v>PAY20260716622742</v>
@@ -3711,13 +3711,13 @@
         <v/>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>PAY-20260716-622742</v>
       </c>
       <c r="O35" t="str">
         <v/>
       </c>
       <c r="P35" t="str">
-        <v>PAY-20260716-622742</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
         <v/>
@@ -3785,10 +3785,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G36" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H36" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I36" t="str">
         <v>PAY20260716725492</v>
@@ -3806,13 +3806,13 @@
         <v/>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>PAY-20260716-725492</v>
       </c>
       <c r="O36" t="str">
         <v/>
       </c>
       <c r="P36" t="str">
-        <v>PAY-20260716-725492</v>
+        <v/>
       </c>
       <c r="Q36" t="str">
         <v/>
@@ -3880,10 +3880,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G37" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H37" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I37" t="str">
         <v>PAY20260716075298</v>
@@ -3901,13 +3901,13 @@
         <v/>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>PAY-20260716-075298</v>
       </c>
       <c r="O37" t="str">
         <v/>
       </c>
       <c r="P37" t="str">
-        <v>PAY-20260716-075298</v>
+        <v/>
       </c>
       <c r="Q37" t="str">
         <v/>
@@ -3975,10 +3975,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G38" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H38" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I38" t="str">
         <v>PAY20260716247057</v>
@@ -3996,13 +3996,13 @@
         <v/>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>PAY-20260716-247057</v>
       </c>
       <c r="O38" t="str">
         <v/>
       </c>
       <c r="P38" t="str">
-        <v>PAY-20260716-247057</v>
+        <v/>
       </c>
       <c r="Q38" t="str">
         <v/>
@@ -4070,10 +4070,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G39" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H39" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I39" t="str">
         <v>PAY20260716168456</v>
@@ -4091,13 +4091,13 @@
         <v/>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>PAY-20260716-168456</v>
       </c>
       <c r="O39" t="str">
         <v/>
       </c>
       <c r="P39" t="str">
-        <v>PAY-20260716-168456</v>
+        <v/>
       </c>
       <c r="Q39" t="str">
         <v/>
@@ -4165,10 +4165,10 @@
         <v>UTIB0000029</v>
       </c>
       <c r="G40" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H40" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I40" t="str">
         <v>PAY20260716097378</v>
@@ -4186,13 +4186,13 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>PAY-20260716-097378</v>
       </c>
       <c r="O40" t="str">
         <v/>
       </c>
       <c r="P40" t="str">
-        <v>PAY-20260716-097378</v>
+        <v/>
       </c>
       <c r="Q40" t="str">
         <v/>
@@ -4260,7 +4260,7 @@
         <v>HDFC0002870</v>
       </c>
       <c r="G41" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H41" t="str">
         <v>N</v>
@@ -4281,13 +4281,13 @@
         <v/>
       </c>
       <c r="N41" t="str">
-        <v/>
+        <v>PAY-20260711-958193</v>
       </c>
       <c r="O41" t="str">
         <v/>
       </c>
       <c r="P41" t="str">
-        <v>PAY-20260711-958193</v>
+        <v/>
       </c>
       <c r="Q41" t="str">
         <v/>
@@ -4355,7 +4355,7 @@
         <v>CNRB0005566</v>
       </c>
       <c r="G42" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H42" t="str">
         <v>N</v>
@@ -4376,13 +4376,13 @@
         <v/>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>PAY-20260708-826638</v>
       </c>
       <c r="O42" t="str">
         <v/>
       </c>
       <c r="P42" t="str">
-        <v>PAY-20260708-826638</v>
+        <v/>
       </c>
       <c r="Q42" t="str">
         <v/>
@@ -4450,7 +4450,7 @@
         <v>CNRB0005566</v>
       </c>
       <c r="G43" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H43" t="str">
         <v>N</v>
@@ -4471,13 +4471,13 @@
         <v/>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>PAY-20260708-863377</v>
       </c>
       <c r="O43" t="str">
         <v/>
       </c>
       <c r="P43" t="str">
-        <v>PAY-20260708-863377</v>
+        <v/>
       </c>
       <c r="Q43" t="str">
         <v/>
@@ -4545,7 +4545,7 @@
         <v>CNRB0005566</v>
       </c>
       <c r="G44" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H44" t="str">
         <v>N</v>
@@ -4566,13 +4566,13 @@
         <v/>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>PAY-20260708-320378</v>
       </c>
       <c r="O44" t="str">
         <v/>
       </c>
       <c r="P44" t="str">
-        <v>PAY-20260708-320378</v>
+        <v/>
       </c>
       <c r="Q44" t="str">
         <v/>
@@ -4640,7 +4640,7 @@
         <v>CNRB0005566</v>
       </c>
       <c r="G45" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H45" t="str">
         <v>N</v>
@@ -4661,13 +4661,13 @@
         <v/>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>PAY-20260708-088577</v>
       </c>
       <c r="O45" t="str">
         <v/>
       </c>
       <c r="P45" t="str">
-        <v>PAY-20260708-088577</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -4735,7 +4735,7 @@
         <v>CNRB0005566</v>
       </c>
       <c r="G46" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H46" t="str">
         <v>N</v>
@@ -4756,13 +4756,13 @@
         <v/>
       </c>
       <c r="N46" t="str">
-        <v/>
+        <v>PAY-20260708-050762</v>
       </c>
       <c r="O46" t="str">
         <v/>
       </c>
       <c r="P46" t="str">
-        <v>PAY-20260708-050762</v>
+        <v/>
       </c>
       <c r="Q46" t="str">
         <v/>
@@ -4830,7 +4830,7 @@
         <v>ICIC0000169</v>
       </c>
       <c r="G47" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H47" t="str">
         <v>N</v>
@@ -4851,13 +4851,13 @@
         <v/>
       </c>
       <c r="N47" t="str">
-        <v/>
+        <v>PAY-20260707-269449</v>
       </c>
       <c r="O47" t="str">
         <v/>
       </c>
       <c r="P47" t="str">
-        <v>PAY-20260707-269449</v>
+        <v/>
       </c>
       <c r="Q47" t="str">
         <v/>
@@ -4925,7 +4925,7 @@
         <v>SBIN0000572</v>
       </c>
       <c r="G48" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H48" t="str">
         <v>N</v>
@@ -4946,13 +4946,13 @@
         <v/>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>PAY-20260701-805832</v>
       </c>
       <c r="O48" t="str">
         <v/>
       </c>
       <c r="P48" t="str">
-        <v>PAY-20260701-805832</v>
+        <v/>
       </c>
       <c r="Q48" t="str">
         <v/>
@@ -5020,7 +5020,7 @@
         <v>CNRB0013128</v>
       </c>
       <c r="G49" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H49" t="str">
         <v>N</v>
@@ -5041,13 +5041,13 @@
         <v/>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>PAY-20260701-319443</v>
       </c>
       <c r="O49" t="str">
         <v/>
       </c>
       <c r="P49" t="str">
-        <v>PAY-20260701-319443</v>
+        <v/>
       </c>
       <c r="Q49" t="str">
         <v/>
@@ -5115,7 +5115,7 @@
         <v>HDFC0000592</v>
       </c>
       <c r="G50" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H50" t="str">
         <v>N</v>
@@ -5136,13 +5136,13 @@
         <v/>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>PAY-20260616-951859</v>
       </c>
       <c r="O50" t="str">
         <v/>
       </c>
       <c r="P50" t="str">
-        <v>PAY-20260616-951859</v>
+        <v/>
       </c>
       <c r="Q50" t="str">
         <v/>
@@ -5210,7 +5210,7 @@
         <v>HDFC0000592</v>
       </c>
       <c r="G51" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H51" t="str">
         <v>N</v>
@@ -5231,13 +5231,13 @@
         <v/>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>PAY-20260616-469779</v>
       </c>
       <c r="O51" t="str">
         <v/>
       </c>
       <c r="P51" t="str">
-        <v>PAY-20260616-469779</v>
+        <v/>
       </c>
       <c r="Q51" t="str">
         <v/>
@@ -5305,7 +5305,7 @@
         <v>HDFC0000592</v>
       </c>
       <c r="G52" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H52" t="str">
         <v>N</v>
@@ -5326,13 +5326,13 @@
         <v/>
       </c>
       <c r="N52" t="str">
-        <v/>
+        <v>PAY-20260616-172942</v>
       </c>
       <c r="O52" t="str">
         <v/>
       </c>
       <c r="P52" t="str">
-        <v>PAY-20260616-172942</v>
+        <v/>
       </c>
       <c r="Q52" t="str">
         <v/>
@@ -5400,7 +5400,7 @@
         <v>HDFC0000212</v>
       </c>
       <c r="G53" t="str">
-        <v>04/09/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="H53" t="str">
         <v>N</v>
@@ -5421,13 +5421,13 @@
         <v/>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>PAY-20260616-639105</v>
       </c>
       <c r="O53" t="str">
         <v/>
       </c>
       <c r="P53" t="str">
-        <v>PAY-20260616-639105</v>
+        <v/>
       </c>
       <c r="Q53" t="str">
         <v/>

--- a/public/AxisBank_Payout_Verification.xlsx
+++ b/public/AxisBank_Payout_Verification.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -67,7 +68,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -374,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE53"/>
+  <dimension ref="A1:AF53"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="29"/>
     <col min="2" max="2" customWidth="1" width="29"/>
@@ -555,7 +556,7 @@
         <v>SBIN0002571</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>09/05/2026</v>
+        <v>05/09/2026</v>
       </c>
       <c r="H2" t="str">
         <v>N</v>
@@ -627,6 +628,9 @@
         <v/>
       </c>
       <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
         <v/>
       </c>
     </row>
@@ -649,8 +653,8 @@
       <c r="F3" t="str">
         <v>BKID0000083</v>
       </c>
-      <c r="G3" t="str">
-        <v>09/05/2026</v>
+      <c r="G3" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H3" t="str">
         <v>N</v>
@@ -722,6 +726,9 @@
         <v/>
       </c>
       <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
         <v/>
       </c>
     </row>
@@ -744,8 +751,8 @@
       <c r="F4" t="str">
         <v>SBIN0005794</v>
       </c>
-      <c r="G4" t="str">
-        <v>09/05/2026</v>
+      <c r="G4" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H4" t="str">
         <v>N</v>
@@ -817,6 +824,9 @@
         <v/>
       </c>
       <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
         <v/>
       </c>
     </row>
@@ -839,8 +849,8 @@
       <c r="F5" t="str">
         <v>HDFC0000485</v>
       </c>
-      <c r="G5" t="str">
-        <v>09/05/2026</v>
+      <c r="G5" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H5" t="str">
         <v>N</v>
@@ -912,6 +922,9 @@
         <v/>
       </c>
       <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
         <v/>
       </c>
     </row>
@@ -934,8 +947,8 @@
       <c r="F6" t="str">
         <v>HDFC0002870</v>
       </c>
-      <c r="G6" t="str">
-        <v>09/05/2026</v>
+      <c r="G6" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H6" t="str">
         <v>N</v>
@@ -1007,6 +1020,9 @@
         <v/>
       </c>
       <c r="AE6" t="str">
+        <v/>
+      </c>
+      <c r="AF6" t="str">
         <v/>
       </c>
     </row>
@@ -1029,8 +1045,8 @@
       <c r="F7" t="str">
         <v>HDFC0000729</v>
       </c>
-      <c r="G7" t="str">
-        <v>09/05/2026</v>
+      <c r="G7" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H7" t="str">
         <v>N</v>
@@ -1102,6 +1118,9 @@
         <v/>
       </c>
       <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
         <v/>
       </c>
     </row>
@@ -1124,8 +1143,8 @@
       <c r="F8" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G8" t="str">
-        <v>09/05/2026</v>
+      <c r="G8" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H8" t="str">
         <v>I</v>
@@ -1197,6 +1216,9 @@
         <v/>
       </c>
       <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
         <v/>
       </c>
     </row>
@@ -1219,8 +1241,8 @@
       <c r="F9" t="str">
         <v>JIOP0000001</v>
       </c>
-      <c r="G9" t="str">
-        <v>09/05/2026</v>
+      <c r="G9" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H9" t="str">
         <v>N</v>
@@ -1292,6 +1314,9 @@
         <v/>
       </c>
       <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
         <v/>
       </c>
     </row>
@@ -1314,8 +1339,8 @@
       <c r="F10" t="str">
         <v>JIOP0000001</v>
       </c>
-      <c r="G10" t="str">
-        <v>09/05/2026</v>
+      <c r="G10" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H10" t="str">
         <v>N</v>
@@ -1387,6 +1412,9 @@
         <v/>
       </c>
       <c r="AE10" t="str">
+        <v/>
+      </c>
+      <c r="AF10" t="str">
         <v/>
       </c>
     </row>
@@ -1409,8 +1437,8 @@
       <c r="F11" t="str">
         <v>HDFC0000729</v>
       </c>
-      <c r="G11" t="str">
-        <v>09/05/2026</v>
+      <c r="G11" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H11" t="str">
         <v>N</v>
@@ -1482,6 +1510,9 @@
         <v/>
       </c>
       <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
         <v/>
       </c>
     </row>
@@ -1504,8 +1535,8 @@
       <c r="F12" t="str">
         <v>SBIN0005794</v>
       </c>
-      <c r="G12" t="str">
-        <v>09/05/2026</v>
+      <c r="G12" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H12" t="str">
         <v>N</v>
@@ -1577,6 +1608,9 @@
         <v/>
       </c>
       <c r="AE12" t="str">
+        <v/>
+      </c>
+      <c r="AF12" t="str">
         <v/>
       </c>
     </row>
@@ -1599,8 +1633,8 @@
       <c r="F13" t="str">
         <v>ICIC0000946</v>
       </c>
-      <c r="G13" t="str">
-        <v>09/05/2026</v>
+      <c r="G13" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H13" t="str">
         <v>N</v>
@@ -1672,6 +1706,9 @@
         <v/>
       </c>
       <c r="AE13" t="str">
+        <v/>
+      </c>
+      <c r="AF13" t="str">
         <v/>
       </c>
     </row>
@@ -1694,8 +1731,8 @@
       <c r="F14" t="str">
         <v>CNRB0013128</v>
       </c>
-      <c r="G14" t="str">
-        <v>09/05/2026</v>
+      <c r="G14" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H14" t="str">
         <v>N</v>
@@ -1767,6 +1804,9 @@
         <v/>
       </c>
       <c r="AE14" t="str">
+        <v/>
+      </c>
+      <c r="AF14" t="str">
         <v/>
       </c>
     </row>
@@ -1789,8 +1829,8 @@
       <c r="F15" t="str">
         <v>CNRB0013128</v>
       </c>
-      <c r="G15" t="str">
-        <v>09/05/2026</v>
+      <c r="G15" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H15" t="str">
         <v>R</v>
@@ -1862,6 +1902,9 @@
         <v/>
       </c>
       <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
         <v/>
       </c>
     </row>
@@ -1884,8 +1927,8 @@
       <c r="F16" t="str">
         <v>CNRB0013128</v>
       </c>
-      <c r="G16" t="str">
-        <v>09/05/2026</v>
+      <c r="G16" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H16" t="str">
         <v>R</v>
@@ -1957,6 +2000,9 @@
         <v/>
       </c>
       <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
         <v/>
       </c>
     </row>
@@ -1979,8 +2025,8 @@
       <c r="F17" t="str">
         <v>CNRB0013128</v>
       </c>
-      <c r="G17" t="str">
-        <v>09/05/2026</v>
+      <c r="G17" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H17" t="str">
         <v>R</v>
@@ -2052,6 +2098,9 @@
         <v/>
       </c>
       <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
         <v/>
       </c>
     </row>
@@ -2074,8 +2123,8 @@
       <c r="F18" t="str">
         <v>SBIN00CARDS</v>
       </c>
-      <c r="G18" t="str">
-        <v>09/05/2026</v>
+      <c r="G18" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H18" t="str">
         <v>N</v>
@@ -2147,6 +2196,9 @@
         <v/>
       </c>
       <c r="AE18" t="str">
+        <v/>
+      </c>
+      <c r="AF18" t="str">
         <v/>
       </c>
     </row>
@@ -2169,8 +2221,8 @@
       <c r="F19" t="str">
         <v>HDFC0002578</v>
       </c>
-      <c r="G19" t="str">
-        <v>09/05/2026</v>
+      <c r="G19" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H19" t="str">
         <v>N</v>
@@ -2242,6 +2294,9 @@
         <v/>
       </c>
       <c r="AE19" t="str">
+        <v/>
+      </c>
+      <c r="AF19" t="str">
         <v/>
       </c>
     </row>
@@ -2264,8 +2319,8 @@
       <c r="F20" t="str">
         <v>ICIC0000946</v>
       </c>
-      <c r="G20" t="str">
-        <v>09/05/2026</v>
+      <c r="G20" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H20" t="str">
         <v>N</v>
@@ -2337,6 +2392,9 @@
         <v/>
       </c>
       <c r="AE20" t="str">
+        <v/>
+      </c>
+      <c r="AF20" t="str">
         <v/>
       </c>
     </row>
@@ -2359,8 +2417,8 @@
       <c r="F21" t="str">
         <v>ICIC0000946</v>
       </c>
-      <c r="G21" t="str">
-        <v>09/05/2026</v>
+      <c r="G21" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H21" t="str">
         <v>N</v>
@@ -2432,6 +2490,9 @@
         <v/>
       </c>
       <c r="AE21" t="str">
+        <v/>
+      </c>
+      <c r="AF21" t="str">
         <v/>
       </c>
     </row>
@@ -2454,8 +2515,8 @@
       <c r="F22" t="str">
         <v>HDFC0002578</v>
       </c>
-      <c r="G22" t="str">
-        <v>09/05/2026</v>
+      <c r="G22" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H22" t="str">
         <v>N</v>
@@ -2527,6 +2588,9 @@
         <v/>
       </c>
       <c r="AE22" t="str">
+        <v/>
+      </c>
+      <c r="AF22" t="str">
         <v/>
       </c>
     </row>
@@ -2549,8 +2613,8 @@
       <c r="F23" t="str">
         <v>SBIN0000055</v>
       </c>
-      <c r="G23" t="str">
-        <v>09/05/2026</v>
+      <c r="G23" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H23" t="str">
         <v>N</v>
@@ -2622,6 +2686,9 @@
         <v/>
       </c>
       <c r="AE23" t="str">
+        <v/>
+      </c>
+      <c r="AF23" t="str">
         <v/>
       </c>
     </row>
@@ -2644,8 +2711,8 @@
       <c r="F24" t="str">
         <v>IDFB0081813</v>
       </c>
-      <c r="G24" t="str">
-        <v>09/05/2026</v>
+      <c r="G24" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H24" t="str">
         <v>N</v>
@@ -2717,6 +2784,9 @@
         <v/>
       </c>
       <c r="AE24" t="str">
+        <v/>
+      </c>
+      <c r="AF24" t="str">
         <v/>
       </c>
     </row>
@@ -2739,8 +2809,8 @@
       <c r="F25" t="str">
         <v>IDFB0081813</v>
       </c>
-      <c r="G25" t="str">
-        <v>09/05/2026</v>
+      <c r="G25" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H25" t="str">
         <v>N</v>
@@ -2812,6 +2882,9 @@
         <v/>
       </c>
       <c r="AE25" t="str">
+        <v/>
+      </c>
+      <c r="AF25" t="str">
         <v/>
       </c>
     </row>
@@ -2834,8 +2907,8 @@
       <c r="F26" t="str">
         <v>IDFB0081813</v>
       </c>
-      <c r="G26" t="str">
-        <v>09/05/2026</v>
+      <c r="G26" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H26" t="str">
         <v>N</v>
@@ -2907,6 +2980,9 @@
         <v/>
       </c>
       <c r="AE26" t="str">
+        <v/>
+      </c>
+      <c r="AF26" t="str">
         <v/>
       </c>
     </row>
@@ -2929,8 +3005,8 @@
       <c r="F27" t="str">
         <v>ICIC0006310</v>
       </c>
-      <c r="G27" t="str">
-        <v>09/05/2026</v>
+      <c r="G27" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H27" t="str">
         <v>N</v>
@@ -3002,6 +3078,9 @@
         <v/>
       </c>
       <c r="AE27" t="str">
+        <v/>
+      </c>
+      <c r="AF27" t="str">
         <v/>
       </c>
     </row>
@@ -3024,8 +3103,8 @@
       <c r="F28" t="str">
         <v>ICIC0006310</v>
       </c>
-      <c r="G28" t="str">
-        <v>09/05/2026</v>
+      <c r="G28" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H28" t="str">
         <v>N</v>
@@ -3097,6 +3176,9 @@
         <v/>
       </c>
       <c r="AE28" t="str">
+        <v/>
+      </c>
+      <c r="AF28" t="str">
         <v/>
       </c>
     </row>
@@ -3119,8 +3201,8 @@
       <c r="F29" t="str">
         <v>ICIC0006310</v>
       </c>
-      <c r="G29" t="str">
-        <v>09/05/2026</v>
+      <c r="G29" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H29" t="str">
         <v>N</v>
@@ -3192,6 +3274,9 @@
         <v/>
       </c>
       <c r="AE29" t="str">
+        <v/>
+      </c>
+      <c r="AF29" t="str">
         <v/>
       </c>
     </row>
@@ -3214,8 +3299,8 @@
       <c r="F30" t="str">
         <v>UTIB0002070</v>
       </c>
-      <c r="G30" t="str">
-        <v>09/05/2026</v>
+      <c r="G30" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H30" t="str">
         <v>I</v>
@@ -3287,6 +3372,9 @@
         <v/>
       </c>
       <c r="AE30" t="str">
+        <v/>
+      </c>
+      <c r="AF30" t="str">
         <v/>
       </c>
     </row>
@@ -3309,8 +3397,8 @@
       <c r="F31" t="str">
         <v>SBIN0000055</v>
       </c>
-      <c r="G31" t="str">
-        <v>09/05/2026</v>
+      <c r="G31" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H31" t="str">
         <v>N</v>
@@ -3382,6 +3470,9 @@
         <v/>
       </c>
       <c r="AE31" t="str">
+        <v/>
+      </c>
+      <c r="AF31" t="str">
         <v/>
       </c>
     </row>
@@ -3404,8 +3495,8 @@
       <c r="F32" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G32" t="str">
-        <v>09/05/2026</v>
+      <c r="G32" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H32" t="str">
         <v>I</v>
@@ -3477,6 +3568,9 @@
         <v/>
       </c>
       <c r="AE32" t="str">
+        <v/>
+      </c>
+      <c r="AF32" t="str">
         <v/>
       </c>
     </row>
@@ -3499,8 +3593,8 @@
       <c r="F33" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G33" t="str">
-        <v>09/05/2026</v>
+      <c r="G33" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H33" t="str">
         <v>I</v>
@@ -3572,6 +3666,9 @@
         <v/>
       </c>
       <c r="AE33" t="str">
+        <v/>
+      </c>
+      <c r="AF33" t="str">
         <v/>
       </c>
     </row>
@@ -3594,8 +3691,8 @@
       <c r="F34" t="str">
         <v>ICIC0000169</v>
       </c>
-      <c r="G34" t="str">
-        <v>09/05/2026</v>
+      <c r="G34" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H34" t="str">
         <v>N</v>
@@ -3667,6 +3764,9 @@
         <v/>
       </c>
       <c r="AE34" t="str">
+        <v/>
+      </c>
+      <c r="AF34" t="str">
         <v/>
       </c>
     </row>
@@ -3689,8 +3789,8 @@
       <c r="F35" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G35" t="str">
-        <v>09/05/2026</v>
+      <c r="G35" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H35" t="str">
         <v>I</v>
@@ -3762,6 +3862,9 @@
         <v/>
       </c>
       <c r="AE35" t="str">
+        <v/>
+      </c>
+      <c r="AF35" t="str">
         <v/>
       </c>
     </row>
@@ -3784,8 +3887,8 @@
       <c r="F36" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G36" t="str">
-        <v>09/05/2026</v>
+      <c r="G36" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H36" t="str">
         <v>I</v>
@@ -3857,6 +3960,9 @@
         <v/>
       </c>
       <c r="AE36" t="str">
+        <v/>
+      </c>
+      <c r="AF36" t="str">
         <v/>
       </c>
     </row>
@@ -3879,8 +3985,8 @@
       <c r="F37" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G37" t="str">
-        <v>09/05/2026</v>
+      <c r="G37" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H37" t="str">
         <v>I</v>
@@ -3952,6 +4058,9 @@
         <v/>
       </c>
       <c r="AE37" t="str">
+        <v/>
+      </c>
+      <c r="AF37" t="str">
         <v/>
       </c>
     </row>
@@ -3974,8 +4083,8 @@
       <c r="F38" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G38" t="str">
-        <v>09/05/2026</v>
+      <c r="G38" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H38" t="str">
         <v>I</v>
@@ -4047,6 +4156,9 @@
         <v/>
       </c>
       <c r="AE38" t="str">
+        <v/>
+      </c>
+      <c r="AF38" t="str">
         <v/>
       </c>
     </row>
@@ -4069,8 +4181,8 @@
       <c r="F39" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G39" t="str">
-        <v>09/05/2026</v>
+      <c r="G39" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H39" t="str">
         <v>I</v>
@@ -4142,6 +4254,9 @@
         <v/>
       </c>
       <c r="AE39" t="str">
+        <v/>
+      </c>
+      <c r="AF39" t="str">
         <v/>
       </c>
     </row>
@@ -4164,8 +4279,8 @@
       <c r="F40" t="str">
         <v>UTIB0000029</v>
       </c>
-      <c r="G40" t="str">
-        <v>09/05/2026</v>
+      <c r="G40" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H40" t="str">
         <v>I</v>
@@ -4237,6 +4352,9 @@
         <v/>
       </c>
       <c r="AE40" t="str">
+        <v/>
+      </c>
+      <c r="AF40" t="str">
         <v/>
       </c>
     </row>
@@ -4259,8 +4377,8 @@
       <c r="F41" t="str">
         <v>HDFC0002870</v>
       </c>
-      <c r="G41" t="str">
-        <v>09/05/2026</v>
+      <c r="G41" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H41" t="str">
         <v>N</v>
@@ -4332,6 +4450,9 @@
         <v/>
       </c>
       <c r="AE41" t="str">
+        <v/>
+      </c>
+      <c r="AF41" t="str">
         <v/>
       </c>
     </row>
@@ -4354,8 +4475,8 @@
       <c r="F42" t="str">
         <v>CNRB0005566</v>
       </c>
-      <c r="G42" t="str">
-        <v>09/05/2026</v>
+      <c r="G42" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H42" t="str">
         <v>N</v>
@@ -4427,6 +4548,9 @@
         <v/>
       </c>
       <c r="AE42" t="str">
+        <v/>
+      </c>
+      <c r="AF42" t="str">
         <v/>
       </c>
     </row>
@@ -4449,8 +4573,8 @@
       <c r="F43" t="str">
         <v>CNRB0005566</v>
       </c>
-      <c r="G43" t="str">
-        <v>09/05/2026</v>
+      <c r="G43" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H43" t="str">
         <v>N</v>
@@ -4522,6 +4646,9 @@
         <v/>
       </c>
       <c r="AE43" t="str">
+        <v/>
+      </c>
+      <c r="AF43" t="str">
         <v/>
       </c>
     </row>
@@ -4544,8 +4671,8 @@
       <c r="F44" t="str">
         <v>CNRB0005566</v>
       </c>
-      <c r="G44" t="str">
-        <v>09/05/2026</v>
+      <c r="G44" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H44" t="str">
         <v>N</v>
@@ -4617,6 +4744,9 @@
         <v/>
       </c>
       <c r="AE44" t="str">
+        <v/>
+      </c>
+      <c r="AF44" t="str">
         <v/>
       </c>
     </row>
@@ -4639,8 +4769,8 @@
       <c r="F45" t="str">
         <v>CNRB0005566</v>
       </c>
-      <c r="G45" t="str">
-        <v>09/05/2026</v>
+      <c r="G45" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H45" t="str">
         <v>N</v>
@@ -4712,6 +4842,9 @@
         <v/>
       </c>
       <c r="AE45" t="str">
+        <v/>
+      </c>
+      <c r="AF45" t="str">
         <v/>
       </c>
     </row>
@@ -4734,8 +4867,8 @@
       <c r="F46" t="str">
         <v>CNRB0005566</v>
       </c>
-      <c r="G46" t="str">
-        <v>09/05/2026</v>
+      <c r="G46" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H46" t="str">
         <v>N</v>
@@ -4807,6 +4940,9 @@
         <v/>
       </c>
       <c r="AE46" t="str">
+        <v/>
+      </c>
+      <c r="AF46" t="str">
         <v/>
       </c>
     </row>
@@ -4829,8 +4965,8 @@
       <c r="F47" t="str">
         <v>ICIC0000169</v>
       </c>
-      <c r="G47" t="str">
-        <v>09/05/2026</v>
+      <c r="G47" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H47" t="str">
         <v>N</v>
@@ -4902,6 +5038,9 @@
         <v/>
       </c>
       <c r="AE47" t="str">
+        <v/>
+      </c>
+      <c r="AF47" t="str">
         <v/>
       </c>
     </row>
@@ -4924,8 +5063,8 @@
       <c r="F48" t="str">
         <v>SBIN0000572</v>
       </c>
-      <c r="G48" t="str">
-        <v>09/05/2026</v>
+      <c r="G48" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H48" t="str">
         <v>N</v>
@@ -4997,6 +5136,9 @@
         <v/>
       </c>
       <c r="AE48" t="str">
+        <v/>
+      </c>
+      <c r="AF48" t="str">
         <v/>
       </c>
     </row>
@@ -5019,8 +5161,8 @@
       <c r="F49" t="str">
         <v>CNRB0013128</v>
       </c>
-      <c r="G49" t="str">
-        <v>09/05/2026</v>
+      <c r="G49" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H49" t="str">
         <v>N</v>
@@ -5092,6 +5234,9 @@
         <v/>
       </c>
       <c r="AE49" t="str">
+        <v/>
+      </c>
+      <c r="AF49" t="str">
         <v/>
       </c>
     </row>
@@ -5114,8 +5259,8 @@
       <c r="F50" t="str">
         <v>HDFC0000592</v>
       </c>
-      <c r="G50" t="str">
-        <v>09/05/2026</v>
+      <c r="G50" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H50" t="str">
         <v>N</v>
@@ -5187,6 +5332,9 @@
         <v/>
       </c>
       <c r="AE50" t="str">
+        <v/>
+      </c>
+      <c r="AF50" t="str">
         <v/>
       </c>
     </row>
@@ -5209,8 +5357,8 @@
       <c r="F51" t="str">
         <v>HDFC0000592</v>
       </c>
-      <c r="G51" t="str">
-        <v>09/05/2026</v>
+      <c r="G51" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H51" t="str">
         <v>N</v>
@@ -5282,6 +5430,9 @@
         <v/>
       </c>
       <c r="AE51" t="str">
+        <v/>
+      </c>
+      <c r="AF51" t="str">
         <v/>
       </c>
     </row>
@@ -5304,8 +5455,8 @@
       <c r="F52" t="str">
         <v>HDFC0000592</v>
       </c>
-      <c r="G52" t="str">
-        <v>09/05/2026</v>
+      <c r="G52" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H52" t="str">
         <v>N</v>
@@ -5377,6 +5528,9 @@
         <v/>
       </c>
       <c r="AE52" t="str">
+        <v/>
+      </c>
+      <c r="AF52" t="str">
         <v/>
       </c>
     </row>
@@ -5399,8 +5553,8 @@
       <c r="F53" t="str">
         <v>HDFC0000212</v>
       </c>
-      <c r="G53" t="str">
-        <v>09/05/2026</v>
+      <c r="G53" s="2" t="str">
+        <v>05/09/2026</v>
       </c>
       <c r="H53" t="str">
         <v>N</v>
@@ -5472,13 +5626,16 @@
         <v/>
       </c>
       <c r="AE53" t="str">
+        <v/>
+      </c>
+      <c r="AF53" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF53"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/AxisBank_Payout_Verification.xlsx
+++ b/public/AxisBank_Payout_Verification.xlsx
@@ -559,7 +559,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I2" t="str">
         <v>PAY20260831658011</v>
@@ -657,7 +657,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I3" t="str">
         <v>PAY20260808003115</v>
@@ -755,7 +755,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H4" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I4" t="str">
         <v>PAY20260805061816</v>
@@ -853,7 +853,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I5" t="str">
         <v>PAY20260805059908</v>
@@ -951,7 +951,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H6" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I6" t="str">
         <v>PAY20260804613052</v>
@@ -1049,7 +1049,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H7" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I7" t="str">
         <v>PAY20260804046652</v>
@@ -1245,7 +1245,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H9" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I9" t="str">
         <v>PAY20260804375695</v>
@@ -1343,7 +1343,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H10" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I10" t="str">
         <v>PAY20260804451179</v>
@@ -1441,7 +1441,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H11" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I11" t="str">
         <v>PAY20260804546420</v>
@@ -1539,7 +1539,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H12" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I12" t="str">
         <v>PAY20260804405930</v>
@@ -1637,7 +1637,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H13" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I13" t="str">
         <v>PAY20260802315857</v>
@@ -1735,7 +1735,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H14" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I14" t="str">
         <v>PAY20260801933762</v>
@@ -1833,7 +1833,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H15" t="str">
-        <v>R</v>
+        <v>I</v>
       </c>
       <c r="I15" t="str">
         <v>PAY20260801762336</v>
@@ -1931,7 +1931,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H16" t="str">
-        <v>R</v>
+        <v>I</v>
       </c>
       <c r="I16" t="str">
         <v>PAY20260731875317</v>
@@ -2029,7 +2029,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H17" t="str">
-        <v>R</v>
+        <v>I</v>
       </c>
       <c r="I17" t="str">
         <v>PAY20260731912652</v>
@@ -2127,7 +2127,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H18" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I18" t="str">
         <v>PAY20260731523707</v>
@@ -2225,7 +2225,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H19" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I19" t="str">
         <v>PAY20260731578132</v>
@@ -2323,7 +2323,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H20" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I20" t="str">
         <v>PAY20260730226073</v>
@@ -2421,7 +2421,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H21" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I21" t="str">
         <v>PAY20260730913804</v>
@@ -2519,7 +2519,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H22" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I22" t="str">
         <v>PAY20260730456908</v>
@@ -2617,7 +2617,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H23" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I23" t="str">
         <v>PAY20260730386586</v>
@@ -2715,7 +2715,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H24" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I24" t="str">
         <v>PAY20260729419157</v>
@@ -2813,7 +2813,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H25" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I25" t="str">
         <v>PAY20260729438891</v>
@@ -2911,7 +2911,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H26" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I26" t="str">
         <v>PAY20260729580331</v>
@@ -3009,7 +3009,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H27" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I27" t="str">
         <v>PAY20260729383214</v>
@@ -3107,7 +3107,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H28" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I28" t="str">
         <v>PAY20260729258687</v>
@@ -3205,7 +3205,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H29" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I29" t="str">
         <v>PAY20260729476921</v>
@@ -3401,7 +3401,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H31" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I31" t="str">
         <v>PAY20260729529558</v>
@@ -3695,7 +3695,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H34" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I34" t="str">
         <v>PAY20260721460795</v>
@@ -4381,7 +4381,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H41" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I41" t="str">
         <v>PAY20260711958193</v>
@@ -4479,7 +4479,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H42" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I42" t="str">
         <v>PAY20260708826638</v>
@@ -4577,7 +4577,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H43" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I43" t="str">
         <v>PAY20260708863377</v>
@@ -4675,7 +4675,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H44" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I44" t="str">
         <v>PAY20260708320378</v>
@@ -4773,7 +4773,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H45" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I45" t="str">
         <v>PAY20260708088577</v>
@@ -4871,7 +4871,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H46" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I46" t="str">
         <v>PAY20260708050762</v>
@@ -4969,7 +4969,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H47" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I47" t="str">
         <v>PAY20260707269449</v>
@@ -5067,7 +5067,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H48" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I48" t="str">
         <v>PAY20260701805832</v>
@@ -5165,7 +5165,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H49" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I49" t="str">
         <v>PAY20260701319443</v>
@@ -5263,7 +5263,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H50" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I50" t="str">
         <v>PAY20260616951859</v>
@@ -5361,7 +5361,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H51" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I51" t="str">
         <v>PAY20260616469779</v>
@@ -5459,7 +5459,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H52" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I52" t="str">
         <v>PAY20260616172942</v>
@@ -5557,7 +5557,7 @@
         <v>05/09/2026</v>
       </c>
       <c r="H53" t="str">
-        <v>N</v>
+        <v>I</v>
       </c>
       <c r="I53" t="str">
         <v>PAY20260616639105</v>
